--- a/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala)</t>
+          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +571,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,7; 70,67</t>
+          <t>62,93; 70,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,88; 71,16</t>
+          <t>63,1; 71,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,88; 69,75</t>
+          <t>63,67; 69,9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +621,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,85; 66,55</t>
+          <t>55,75; 66,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,09; 69,33</t>
+          <t>60,92; 69,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,8; 66,48</t>
+          <t>57,58; 66,44</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,24; 70,4</t>
+          <t>63,99; 70,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,51; 68,29</t>
+          <t>61,78; 68,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,61; 68,47</t>
+          <t>63,64; 68,39</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,88; 70,82</t>
+          <t>62,73; 70,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,48; 73,25</t>
+          <t>65,44; 72,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,58; 70,76</t>
+          <t>65,31; 70,62</t>
         </is>
       </c>
     </row>
@@ -771,24 +771,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>65,29; 72,56</t>
+          <t>64,61; 71,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,73; 69,5</t>
+          <t>59,92; 69,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,08; 69,56</t>
+          <t>63,14; 69,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +821,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,8; 72,22</t>
+          <t>65,24; 72,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,54; 74,21</t>
+          <t>66,47; 73,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,81; 72,14</t>
+          <t>66,48; 71,97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,5</t>
+          <t>65,69; 72,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,32; 67,7</t>
+          <t>57,37; 67,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,93; 68,83</t>
+          <t>61,67; 68,66</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,03; 65,64</t>
+          <t>60,18; 65,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,93; 62,54</t>
+          <t>57,78; 62,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,53; 63,28</t>
+          <t>59,36; 63,14</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62,53; 66,91</t>
+          <t>62,67; 66,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,82; 66,11</t>
+          <t>62,74; 66,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,48; 66,02</t>
+          <t>63,26; 66,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,93; 70,66</t>
+          <t>62,73; 70,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,32</t>
+          <t>63,09; 71,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,67; 69,9</t>
+          <t>64,06; 69,83</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,75; 66,42</t>
+          <t>55,52; 66,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60,92; 69,7</t>
+          <t>61,0; 69,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57,58; 66,44</t>
+          <t>58,28; 66,46</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,99; 70,32</t>
+          <t>64,07; 70,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,78; 68,21</t>
+          <t>60,92; 67,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,64; 68,39</t>
+          <t>63,34; 68,16</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,73; 70,89</t>
+          <t>62,77; 70,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,44; 72,84</t>
+          <t>65,24; 72,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,31; 70,62</t>
+          <t>65,39; 70,61</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,61; 71,93</t>
+          <t>64,97; 72,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,92; 69,61</t>
+          <t>59,64; 69,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,14; 69,21</t>
+          <t>62,99; 69,24</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,24; 72,65</t>
+          <t>64,59; 72,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,47; 73,75</t>
+          <t>66,64; 73,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,48; 71,97</t>
+          <t>66,55; 72,05</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65,69; 72,03</t>
+          <t>66,16; 72,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,37; 67,65</t>
+          <t>57,64; 67,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61,67; 68,66</t>
+          <t>62,51; 68,45</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>60,18; 65,84</t>
+          <t>59,92; 65,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,78; 62,64</t>
+          <t>57,8; 62,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,36; 63,14</t>
+          <t>59,37; 63,16</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62,67; 66,91</t>
+          <t>62,34; 66,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,74; 66,11</t>
+          <t>62,85; 66,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,26; 66,08</t>
+          <t>63,3; 66,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
@@ -489,18 +489,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>66,78</t>
+          <t>67,14</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>66,97</t>
+          <t>66,02</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66,89</t>
+          <t>66,65</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>62,73; 70,48</t>
+          <t>62,99; 71,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,09; 71,45</t>
+          <t>62,15; 69,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,06; 69,83</t>
+          <t>63,87; 69,44</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>60,9</t>
+          <t>65,04</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,84</t>
+          <t>65,13</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62,79</t>
+          <t>65,08</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,52; 66,45</t>
+          <t>61,39; 69,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,0; 69,81</t>
+          <t>61,64; 68,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,28; 66,46</t>
+          <t>62,34; 68,29</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>67,27</t>
+          <t>65,0</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>64,97</t>
+          <t>67,24</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66,0</t>
+          <t>66,06</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,07; 70,62</t>
+          <t>61,68; 68,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,92; 67,82</t>
+          <t>64,25; 70,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,34; 68,16</t>
+          <t>63,75; 68,52</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>66,67</t>
+          <t>69,01</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68,86</t>
+          <t>66,72</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67,92</t>
+          <t>67,97</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,77; 70,22</t>
+          <t>65,48; 73,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,24; 72,8</t>
+          <t>62,93; 70,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65,39; 70,61</t>
+          <t>65,58; 70,84</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>68,39</t>
+          <t>64,82</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64,9</t>
+          <t>68,37</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66,41</t>
+          <t>66,39</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,97; 72,16</t>
+          <t>59,39; 69,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>59,64; 69,68</t>
+          <t>65,38; 72,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,99; 69,24</t>
+          <t>63,03; 69,42</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>68,49</t>
+          <t>69,59</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70,09</t>
+          <t>68,27</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69,29</t>
+          <t>68,89</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,59; 72,4</t>
+          <t>66,16; 73,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,64; 73,96</t>
+          <t>64,47; 71,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,55; 72,05</t>
+          <t>66,39; 71,69</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>69,17</t>
+          <t>66,1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>63,94</t>
+          <t>69,47</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66,18</t>
+          <t>67,64</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>66,16; 72,26</t>
+          <t>62,82; 69,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,67</t>
+          <t>66,41; 72,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62,51; 68,45</t>
+          <t>65,22; 69,95</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62,65</t>
+          <t>60,09</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59,99</t>
+          <t>62,8</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61,2</t>
+          <t>61,36</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,92; 65,33</t>
+          <t>58,08; 62,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,8; 62,51</t>
+          <t>60,05; 65,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59,37; 63,16</t>
+          <t>59,59; 63,49</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>65,35</t>
+          <t>64,93</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>64,57</t>
+          <t>66,28</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64,93</t>
+          <t>65,55</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>62,34; 66,79</t>
+          <t>63,64; 66,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62,85; 66,07</t>
+          <t>65,07; 67,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63,3; 66,01</t>
+          <t>64,65; 66,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Provincia-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 49,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>67,14</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>66,02</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66,65</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>67.1398886217009</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>66.01993620309787</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>66.6499737988495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>62,99; 71,31</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>62,15; 69,73</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63,87; 69,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>62.99039252773872</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>62.14891018124825</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>63.87003642605282</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>71.31498944053234</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>69.73312800531559</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>69.44395549216905</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Cádiz</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>65,04</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>65,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>61,39; 69,62</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>61,64; 68,78</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62,34; 68,29</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>65.04076878701861</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>65.12613157458715</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>65.07786315838062</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>65,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>67,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>66,06</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>61.38530363613989</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>61.64271403625315</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>62.33643855979933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>61,68; 68,41</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64,25; 70,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63,75; 68,52</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>69.61644530065035</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>68.78270718153109</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>68.28883523288137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,149 +661,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>69,01</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66,72</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>67,97</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>64.996925005587</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>67.24397124536378</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>66.05921400143615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>65,48; 73,34</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>62,93; 70,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65,58; 70,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>61.68063179720845</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>64.2536909334047</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>63.75454721002492</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Huelva</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>68.40548567990946</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>70.31342134946973</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>68.51577100003369</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>64,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>68,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>66,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>59,39; 69,25</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>65,38; 72,42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63,03; 69,42</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>69.00595736870631</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>66.72485612111034</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>67.97079214538985</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Jaén</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>69,59</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>68,27</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>65.48407364045399</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>62.93463233994772</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>65.58445545223505</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>66,16; 73,81</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>64,47; 71,88</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>66,39; 71,69</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>73.34098122199488</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>70.91458809298589</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>70.8391727843471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -846,147 +771,272 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>66,1</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>69,47</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>67,64</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>64.81717448002374</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>68.37304432749765</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>66.38716207532779</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>62,82; 69,23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>66,41; 72,81</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65,22; 69,95</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>59.39141752891662</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>65.37826364074296</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>63.03026584628554</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>69.25155365639775</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>72.42165846467067</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>69.41958204177246</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>60,09</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>62,8</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>61,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>58,08; 62,7</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>60,05; 65,83</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>59,59; 63,49</t>
-        </is>
+      <c r="C19" s="5" t="n">
+        <v>69.59226903773515</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>68.27211690578866</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>68.89280349357722</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>64,93</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>66,28</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>65,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>66.16407654923853</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>64.47101451821786</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>66.39022650802984</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>63,64; 66,39</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>65,07; 67,66</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>64,65; 66,49</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>73.81313729647526</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>71.87561829650025</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>71.68827420562283</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>66.09752344893379</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>69.47186020485269</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>67.63632204223786</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>62.81785125571483</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>66.40753378426041</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>65.21730645087345</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>69.22632653682807</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>72.81444218010148</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>69.95349181789656</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>60.08751326680379</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>62.80131399990032</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>61.35548643220913</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>58.08375579576695</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>60.04999859645775</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>59.59185279064613</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>62.70427617849371</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>65.82756659288856</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>63.49487805377324</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>64.92732094460014</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>66.28067204261059</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>65.54846297643974</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>63.64034898981852</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>65.06789259723863</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>64.65044445765709</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>66.38548833554718</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>67.65564031366436</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>66.48919769510343</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -994,16 +1044,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
